--- a/2022 data/excel_outputs/194_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/194_boothwise_data.xlsx
@@ -14,354 +14,1338 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="466">
   <si>
     <t>AC 194 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>######## ####### ### ####### #### #### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ####### ## ##### #### #######</t>
-  </si>
-  <si>
-    <t>######## ####### ###### ## ##### #### ####</t>
-  </si>
-  <si>
-    <t>######## ####### ######## ###</t>
-  </si>
-  <si>
-    <t>######## ####### ####### ####</t>
-  </si>
-  <si>
-    <t>######## ####### #######</t>
-  </si>
-  <si>
-    <t>######## ####### ######</t>
-  </si>
-  <si>
-    <t>###### ### ##### ##### ###</t>
-  </si>
-  <si>
-    <t>###### ### ##### ####</t>
-  </si>
-  <si>
-    <t>######## ####### #### #####</t>
-  </si>
-  <si>
-    <t>######## ####### ####</t>
-  </si>
-  <si>
-    <t>######## ####### ####### ###</t>
-  </si>
-  <si>
-    <t>######## ####### ##### #### #####</t>
-  </si>
-  <si>
-    <t>######## ####### #####</t>
-  </si>
-  <si>
-    <t>######## ####### ########## ###</t>
-  </si>
-  <si>
-    <t>######## ####### #### #######</t>
-  </si>
-  <si>
-    <t>######## ####### ####### #####</t>
-  </si>
-  <si>
-    <t>######## ####### ######## #### #######</t>
-  </si>
-  <si>
-    <t>######### ##### ####### #######</t>
-  </si>
-  <si>
-    <t>##### ######## ####### ######</t>
-  </si>
-  <si>
-    <t>######## ###### ##### #### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ###########</t>
-  </si>
-  <si>
-    <t>######## ####### ########</t>
-  </si>
-  <si>
-    <t>###### ## #####</t>
-  </si>
-  <si>
-    <t>######## ####### #########</t>
-  </si>
-  <si>
-    <t>####### ###### ##</t>
-  </si>
-  <si>
-    <t>##### ######## ####### #######</t>
-  </si>
-  <si>
-    <t>###### ## #########</t>
-  </si>
-  <si>
-    <t>###### ## #### #######</t>
-  </si>
-  <si>
-    <t>######## ####### ###### #####</t>
-  </si>
-  <si>
-    <t>##### ######## ####### ############</t>
-  </si>
-  <si>
-    <t>######## ####### ###### #### #### ###### ###### ###</t>
-  </si>
-  <si>
-    <t>######## ####### #### #### #### ######## #### ####</t>
-  </si>
-  <si>
-    <t>######## ####### ###### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ######## #### ########</t>
-  </si>
-  <si>
-    <t>##### ######## ######## ####### #####</t>
-  </si>
-  <si>
-    <t>######## ####### #### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ##########</t>
-  </si>
-  <si>
-    <t>######## ####### ##### ####</t>
-  </si>
-  <si>
-    <t>###### ### ##### ##### ####</t>
-  </si>
-  <si>
-    <t>######## ###### ### ######</t>
-  </si>
-  <si>
-    <t>###### ### ##### ### #####</t>
-  </si>
-  <si>
-    <t>###### ### ##### ##### #####</t>
-  </si>
-  <si>
-    <t>######## ####### ##### #####</t>
-  </si>
-  <si>
-    <t>###### ### ##### ##########</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ###### ## #############</t>
-  </si>
-  <si>
-    <t>######## ####### #############</t>
-  </si>
-  <si>
-    <t>###### ### ##### #####</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ####### #### ####</t>
-  </si>
-  <si>
-    <t>##### ######## ####### ########### ######</t>
-  </si>
-  <si>
-    <t>###### ### ##### ### ### #### ######## ######## #### #####</t>
-  </si>
-  <si>
-    <t>########### ##### ##### ######</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #### ######</t>
-  </si>
-  <si>
-    <t>###### ##### ###### ##### ######</t>
-  </si>
-  <si>
-    <t>###### #### ##### ##### #### ###</t>
-  </si>
-  <si>
-    <t>######### ##### ########</t>
-  </si>
-  <si>
-    <t>### #### ######## ## ## ## ###</t>
-  </si>
-  <si>
-    <t>###### #### ##### ##### ######## ### ##### ;####0#0ddh</t>
-  </si>
-  <si>
-    <t>##0 #####0##0 ##### ####</t>
-  </si>
-  <si>
-    <t>####### ## ######## ##### ###### ######</t>
-  </si>
-  <si>
-    <t>##### #### #### ###### ######## #########</t>
-  </si>
-  <si>
-    <t>######## ####### ####### ######</t>
-  </si>
-  <si>
-    <t>##### #### ##### ####### ###### ##### ##########</t>
-  </si>
-  <si>
-    <t>######## ####### ##### ###</t>
-  </si>
-  <si>
-    <t>###### ####### #0##0 ###### ##########</t>
-  </si>
-  <si>
-    <t>##### #### ##### ####### #0 ##0 ##### #####</t>
-  </si>
-  <si>
-    <t>##### ######## ######## ########</t>
-  </si>
-  <si>
-    <t>######### ##### ####### ########</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##### #### ###### ####</t>
-  </si>
-  <si>
-    <t>####### ##### ##### ######</t>
-  </si>
-  <si>
-    <t>####### #### ######## ####### ##### ###</t>
-  </si>
-  <si>
-    <t>######## ####### #### ####</t>
-  </si>
-  <si>
-    <t>##### ##### ######## ######## #### ##### #####</t>
-  </si>
-  <si>
-    <t>######## ##### ######## #########</t>
-  </si>
-  <si>
-    <t>##### ### ########</t>
-  </si>
-  <si>
-    <t>##### ######### ####### #######</t>
-  </si>
-  <si>
-    <t>######## ####### #### ##### #####</t>
-  </si>
-  <si>
-    <t>######## ####### ##### #### ##### ####### ########### ######## ####### ### #####</t>
-  </si>
-  <si>
-    <t>##### ### ##### ######### ##### #####</t>
-  </si>
-  <si>
-    <t>### ###### ########## #### ###</t>
-  </si>
-  <si>
-    <t>##0 ####### ###### ##### ##0 ##0 #### #####</t>
-  </si>
-  <si>
-    <t>##### ######## ####### #########</t>
-  </si>
-  <si>
-    <t>###### ###### ###### ######## ######</t>
-  </si>
-  <si>
-    <t>##### ###### ######## ######## #########</t>
-  </si>
-  <si>
-    <t>######## ###### ######</t>
-  </si>
-  <si>
-    <t>##### ######## ######## ######</t>
-  </si>
-  <si>
-    <t>###### ######## ###### ##### #####</t>
-  </si>
-  <si>
-    <t>######## #### ########</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### ##########</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##########</t>
-  </si>
-  <si>
-    <t>####### ######## ####### ######</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ######## ######</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ###### ######## ##### #######</t>
-  </si>
-  <si>
-    <t>##### ###### ######## #####</t>
-  </si>
-  <si>
-    <t>##### ###### ### ##### #####</t>
-  </si>
-  <si>
-    <t>########## ##### ##### ##########</t>
-  </si>
-  <si>
-    <t>##### ##### ########### ##########</t>
-  </si>
-  <si>
-    <t>######## ####### ###### ####</t>
-  </si>
-  <si>
-    <t>#### ###### ###### #####</t>
-  </si>
-  <si>
-    <t>#### ###### ###### ##### ######</t>
-  </si>
-  <si>
-    <t>###### ###### ### ##### #######</t>
-  </si>
-  <si>
-    <t>##### ###### ### ##### #######</t>
-  </si>
-  <si>
-    <t>###### ###########</t>
-  </si>
-  <si>
-    <t>###### ### ##### ########</t>
-  </si>
-  <si>
-    <t>##### ##### ######## ######## #### ##### ########</t>
-  </si>
-  <si>
-    <t>######## ####### #### ###</t>
-  </si>
-  <si>
-    <t>##### ######## ####### ########</t>
-  </si>
-  <si>
-    <t>######## ####### ####### ########</t>
-  </si>
-  <si>
-    <t>######## ####### #### ## #### ##### #####</t>
-  </si>
-  <si>
-    <t>######## ####### ##### #### #### ######</t>
-  </si>
-  <si>
-    <t>######## ######## #### ###</t>
-  </si>
-  <si>
-    <t>######## ####### ######## #######</t>
-  </si>
-  <si>
-    <t>######## ####### ###### ###</t>
+    <t>BOOTH 1</t>
+  </si>
+  <si>
+    <t>BOOTH 2</t>
+  </si>
+  <si>
+    <t>BOOTH 3</t>
+  </si>
+  <si>
+    <t>BOOTH 4</t>
+  </si>
+  <si>
+    <t>BOOTH 5</t>
+  </si>
+  <si>
+    <t>BOOTH 6</t>
+  </si>
+  <si>
+    <t>BOOTH 7</t>
+  </si>
+  <si>
+    <t>BOOTH 8</t>
+  </si>
+  <si>
+    <t>BOOTH 9</t>
+  </si>
+  <si>
+    <t>BOOTH 10</t>
+  </si>
+  <si>
+    <t>BOOTH 11</t>
+  </si>
+  <si>
+    <t>BOOTH 12</t>
+  </si>
+  <si>
+    <t>BOOTH 13</t>
+  </si>
+  <si>
+    <t>BOOTH 14</t>
+  </si>
+  <si>
+    <t>BOOTH 15</t>
+  </si>
+  <si>
+    <t>BOOTH 16</t>
+  </si>
+  <si>
+    <t>BOOTH 17</t>
+  </si>
+  <si>
+    <t>BOOTH 18</t>
+  </si>
+  <si>
+    <t>BOOTH 19</t>
+  </si>
+  <si>
+    <t>BOOTH 20</t>
+  </si>
+  <si>
+    <t>BOOTH 21</t>
+  </si>
+  <si>
+    <t>BOOTH 22</t>
+  </si>
+  <si>
+    <t>BOOTH 23</t>
+  </si>
+  <si>
+    <t>BOOTH 24</t>
+  </si>
+  <si>
+    <t>BOOTH 25</t>
+  </si>
+  <si>
+    <t>BOOTH 26</t>
+  </si>
+  <si>
+    <t>BOOTH 27</t>
+  </si>
+  <si>
+    <t>BOOTH 28</t>
+  </si>
+  <si>
+    <t>BOOTH 29</t>
+  </si>
+  <si>
+    <t>BOOTH 30</t>
+  </si>
+  <si>
+    <t>BOOTH 31</t>
+  </si>
+  <si>
+    <t>BOOTH 32</t>
+  </si>
+  <si>
+    <t>BOOTH 33</t>
+  </si>
+  <si>
+    <t>BOOTH 34</t>
+  </si>
+  <si>
+    <t>BOOTH 35</t>
+  </si>
+  <si>
+    <t>BOOTH 36</t>
+  </si>
+  <si>
+    <t>BOOTH 37</t>
+  </si>
+  <si>
+    <t>BOOTH 38</t>
+  </si>
+  <si>
+    <t>BOOTH 39</t>
+  </si>
+  <si>
+    <t>BOOTH 40</t>
+  </si>
+  <si>
+    <t>BOOTH 41</t>
+  </si>
+  <si>
+    <t>BOOTH 42</t>
+  </si>
+  <si>
+    <t>BOOTH 43</t>
+  </si>
+  <si>
+    <t>BOOTH 44</t>
+  </si>
+  <si>
+    <t>BOOTH 45</t>
+  </si>
+  <si>
+    <t>BOOTH 46</t>
+  </si>
+  <si>
+    <t>BOOTH 47</t>
+  </si>
+  <si>
+    <t>BOOTH 48</t>
+  </si>
+  <si>
+    <t>BOOTH 49</t>
+  </si>
+  <si>
+    <t>BOOTH 50</t>
+  </si>
+  <si>
+    <t>BOOTH 51</t>
+  </si>
+  <si>
+    <t>BOOTH 52</t>
+  </si>
+  <si>
+    <t>BOOTH 53</t>
+  </si>
+  <si>
+    <t>BOOTH 54</t>
+  </si>
+  <si>
+    <t>BOOTH 55</t>
+  </si>
+  <si>
+    <t>BOOTH 56</t>
+  </si>
+  <si>
+    <t>BOOTH 57</t>
+  </si>
+  <si>
+    <t>BOOTH 58</t>
+  </si>
+  <si>
+    <t>BOOTH 59</t>
+  </si>
+  <si>
+    <t>BOOTH 60</t>
+  </si>
+  <si>
+    <t>BOOTH 61</t>
+  </si>
+  <si>
+    <t>BOOTH 62</t>
+  </si>
+  <si>
+    <t>BOOTH 63</t>
+  </si>
+  <si>
+    <t>BOOTH 64</t>
+  </si>
+  <si>
+    <t>BOOTH 65</t>
+  </si>
+  <si>
+    <t>BOOTH 66</t>
+  </si>
+  <si>
+    <t>BOOTH 67</t>
+  </si>
+  <si>
+    <t>BOOTH 68</t>
+  </si>
+  <si>
+    <t>BOOTH 69</t>
+  </si>
+  <si>
+    <t>BOOTH 70</t>
+  </si>
+  <si>
+    <t>BOOTH 71</t>
+  </si>
+  <si>
+    <t>BOOTH 72</t>
+  </si>
+  <si>
+    <t>BOOTH 73</t>
+  </si>
+  <si>
+    <t>BOOTH 74</t>
+  </si>
+  <si>
+    <t>BOOTH 75</t>
+  </si>
+  <si>
+    <t>BOOTH 76</t>
+  </si>
+  <si>
+    <t>BOOTH 77</t>
+  </si>
+  <si>
+    <t>BOOTH 78</t>
+  </si>
+  <si>
+    <t>BOOTH 79</t>
+  </si>
+  <si>
+    <t>BOOTH 80</t>
+  </si>
+  <si>
+    <t>BOOTH 81</t>
+  </si>
+  <si>
+    <t>BOOTH 82</t>
+  </si>
+  <si>
+    <t>BOOTH 83</t>
+  </si>
+  <si>
+    <t>BOOTH 84</t>
+  </si>
+  <si>
+    <t>BOOTH 85</t>
+  </si>
+  <si>
+    <t>BOOTH 86</t>
+  </si>
+  <si>
+    <t>BOOTH 87</t>
+  </si>
+  <si>
+    <t>BOOTH 88</t>
+  </si>
+  <si>
+    <t>BOOTH 89</t>
+  </si>
+  <si>
+    <t>BOOTH 90</t>
+  </si>
+  <si>
+    <t>BOOTH 91</t>
+  </si>
+  <si>
+    <t>BOOTH 92</t>
+  </si>
+  <si>
+    <t>BOOTH 93</t>
+  </si>
+  <si>
+    <t>BOOTH 94</t>
+  </si>
+  <si>
+    <t>BOOTH 95</t>
+  </si>
+  <si>
+    <t>BOOTH 96</t>
+  </si>
+  <si>
+    <t>BOOTH 97</t>
+  </si>
+  <si>
+    <t>BOOTH 98</t>
+  </si>
+  <si>
+    <t>BOOTH 99</t>
+  </si>
+  <si>
+    <t>BOOTH 100</t>
+  </si>
+  <si>
+    <t>BOOTH 101</t>
+  </si>
+  <si>
+    <t>BOOTH 102</t>
+  </si>
+  <si>
+    <t>BOOTH 103</t>
+  </si>
+  <si>
+    <t>BOOTH 104</t>
+  </si>
+  <si>
+    <t>BOOTH 105</t>
+  </si>
+  <si>
+    <t>BOOTH 106</t>
+  </si>
+  <si>
+    <t>BOOTH 107</t>
+  </si>
+  <si>
+    <t>BOOTH 108</t>
+  </si>
+  <si>
+    <t>BOOTH 109</t>
+  </si>
+  <si>
+    <t>BOOTH 110</t>
+  </si>
+  <si>
+    <t>BOOTH 111</t>
+  </si>
+  <si>
+    <t>BOOTH 112</t>
+  </si>
+  <si>
+    <t>BOOTH 113</t>
+  </si>
+  <si>
+    <t>BOOTH 114</t>
+  </si>
+  <si>
+    <t>BOOTH 115</t>
+  </si>
+  <si>
+    <t>BOOTH 116</t>
+  </si>
+  <si>
+    <t>BOOTH 117</t>
+  </si>
+  <si>
+    <t>BOOTH 118</t>
+  </si>
+  <si>
+    <t>BOOTH 119</t>
+  </si>
+  <si>
+    <t>BOOTH 120</t>
+  </si>
+  <si>
+    <t>BOOTH 121</t>
+  </si>
+  <si>
+    <t>BOOTH 122</t>
+  </si>
+  <si>
+    <t>BOOTH 123</t>
+  </si>
+  <si>
+    <t>BOOTH 124</t>
+  </si>
+  <si>
+    <t>BOOTH 125</t>
+  </si>
+  <si>
+    <t>BOOTH 126</t>
+  </si>
+  <si>
+    <t>BOOTH 127</t>
+  </si>
+  <si>
+    <t>BOOTH 128</t>
+  </si>
+  <si>
+    <t>BOOTH 129</t>
+  </si>
+  <si>
+    <t>BOOTH 130</t>
+  </si>
+  <si>
+    <t>BOOTH 131</t>
+  </si>
+  <si>
+    <t>BOOTH 132</t>
+  </si>
+  <si>
+    <t>BOOTH 133</t>
+  </si>
+  <si>
+    <t>BOOTH 134</t>
+  </si>
+  <si>
+    <t>BOOTH 135</t>
+  </si>
+  <si>
+    <t>BOOTH 136</t>
+  </si>
+  <si>
+    <t>BOOTH 137</t>
+  </si>
+  <si>
+    <t>BOOTH 138</t>
+  </si>
+  <si>
+    <t>BOOTH 139</t>
+  </si>
+  <si>
+    <t>BOOTH 140</t>
+  </si>
+  <si>
+    <t>BOOTH 141</t>
+  </si>
+  <si>
+    <t>BOOTH 142</t>
+  </si>
+  <si>
+    <t>BOOTH 143</t>
+  </si>
+  <si>
+    <t>BOOTH 144</t>
+  </si>
+  <si>
+    <t>BOOTH 145</t>
+  </si>
+  <si>
+    <t>BOOTH 146</t>
+  </si>
+  <si>
+    <t>BOOTH 147</t>
+  </si>
+  <si>
+    <t>BOOTH 148</t>
+  </si>
+  <si>
+    <t>BOOTH 149</t>
+  </si>
+  <si>
+    <t>BOOTH 150</t>
+  </si>
+  <si>
+    <t>BOOTH 151</t>
+  </si>
+  <si>
+    <t>BOOTH 152</t>
+  </si>
+  <si>
+    <t>BOOTH 153</t>
+  </si>
+  <si>
+    <t>BOOTH 154</t>
+  </si>
+  <si>
+    <t>BOOTH 155</t>
+  </si>
+  <si>
+    <t>BOOTH 156</t>
+  </si>
+  <si>
+    <t>BOOTH 157</t>
+  </si>
+  <si>
+    <t>BOOTH 158</t>
+  </si>
+  <si>
+    <t>BOOTH 159</t>
+  </si>
+  <si>
+    <t>BOOTH 160</t>
+  </si>
+  <si>
+    <t>BOOTH 161</t>
+  </si>
+  <si>
+    <t>BOOTH 162</t>
+  </si>
+  <si>
+    <t>BOOTH 163</t>
+  </si>
+  <si>
+    <t>BOOTH 164</t>
+  </si>
+  <si>
+    <t>BOOTH 165</t>
+  </si>
+  <si>
+    <t>BOOTH 166</t>
+  </si>
+  <si>
+    <t>BOOTH 167</t>
+  </si>
+  <si>
+    <t>BOOTH 168</t>
+  </si>
+  <si>
+    <t>BOOTH 169</t>
+  </si>
+  <si>
+    <t>BOOTH 170</t>
+  </si>
+  <si>
+    <t>BOOTH 171</t>
+  </si>
+  <si>
+    <t>BOOTH 172</t>
+  </si>
+  <si>
+    <t>BOOTH 173</t>
+  </si>
+  <si>
+    <t>BOOTH 174</t>
+  </si>
+  <si>
+    <t>BOOTH 175</t>
+  </si>
+  <si>
+    <t>BOOTH 176</t>
+  </si>
+  <si>
+    <t>BOOTH 177</t>
+  </si>
+  <si>
+    <t>BOOTH 178</t>
+  </si>
+  <si>
+    <t>BOOTH 179</t>
+  </si>
+  <si>
+    <t>BOOTH 180</t>
+  </si>
+  <si>
+    <t>BOOTH 181</t>
+  </si>
+  <si>
+    <t>BOOTH 182</t>
+  </si>
+  <si>
+    <t>BOOTH 183</t>
+  </si>
+  <si>
+    <t>BOOTH 184</t>
+  </si>
+  <si>
+    <t>BOOTH 185</t>
+  </si>
+  <si>
+    <t>BOOTH 186</t>
+  </si>
+  <si>
+    <t>BOOTH 187</t>
+  </si>
+  <si>
+    <t>BOOTH 188</t>
+  </si>
+  <si>
+    <t>BOOTH 189</t>
+  </si>
+  <si>
+    <t>BOOTH 190</t>
+  </si>
+  <si>
+    <t>BOOTH 191</t>
+  </si>
+  <si>
+    <t>BOOTH 192</t>
+  </si>
+  <si>
+    <t>BOOTH 193</t>
+  </si>
+  <si>
+    <t>BOOTH 194</t>
+  </si>
+  <si>
+    <t>BOOTH 195</t>
+  </si>
+  <si>
+    <t>BOOTH 196</t>
+  </si>
+  <si>
+    <t>BOOTH 197</t>
+  </si>
+  <si>
+    <t>BOOTH 198</t>
+  </si>
+  <si>
+    <t>BOOTH 199</t>
+  </si>
+  <si>
+    <t>BOOTH 200</t>
+  </si>
+  <si>
+    <t>BOOTH 201</t>
+  </si>
+  <si>
+    <t>BOOTH 202</t>
+  </si>
+  <si>
+    <t>BOOTH 203</t>
+  </si>
+  <si>
+    <t>BOOTH 204</t>
+  </si>
+  <si>
+    <t>BOOTH 205</t>
+  </si>
+  <si>
+    <t>BOOTH 206</t>
+  </si>
+  <si>
+    <t>BOOTH 207</t>
+  </si>
+  <si>
+    <t>BOOTH 208</t>
+  </si>
+  <si>
+    <t>BOOTH 209</t>
+  </si>
+  <si>
+    <t>BOOTH 210</t>
+  </si>
+  <si>
+    <t>BOOTH 211</t>
+  </si>
+  <si>
+    <t>BOOTH 212</t>
+  </si>
+  <si>
+    <t>BOOTH 213</t>
+  </si>
+  <si>
+    <t>BOOTH 214</t>
+  </si>
+  <si>
+    <t>BOOTH 215</t>
+  </si>
+  <si>
+    <t>BOOTH 216</t>
+  </si>
+  <si>
+    <t>BOOTH 217</t>
+  </si>
+  <si>
+    <t>BOOTH 218</t>
+  </si>
+  <si>
+    <t>BOOTH 219</t>
+  </si>
+  <si>
+    <t>BOOTH 220</t>
+  </si>
+  <si>
+    <t>BOOTH 221</t>
+  </si>
+  <si>
+    <t>BOOTH 222</t>
+  </si>
+  <si>
+    <t>BOOTH 223</t>
+  </si>
+  <si>
+    <t>BOOTH 224</t>
+  </si>
+  <si>
+    <t>BOOTH 225</t>
+  </si>
+  <si>
+    <t>BOOTH 226</t>
+  </si>
+  <si>
+    <t>BOOTH 227</t>
+  </si>
+  <si>
+    <t>BOOTH 228</t>
+  </si>
+  <si>
+    <t>BOOTH 229</t>
+  </si>
+  <si>
+    <t>BOOTH 230</t>
+  </si>
+  <si>
+    <t>BOOTH 231</t>
+  </si>
+  <si>
+    <t>BOOTH 232</t>
+  </si>
+  <si>
+    <t>BOOTH 233</t>
+  </si>
+  <si>
+    <t>BOOTH 234</t>
+  </si>
+  <si>
+    <t>BOOTH 235</t>
+  </si>
+  <si>
+    <t>BOOTH 236</t>
+  </si>
+  <si>
+    <t>BOOTH 237</t>
+  </si>
+  <si>
+    <t>BOOTH 238</t>
+  </si>
+  <si>
+    <t>BOOTH 239</t>
+  </si>
+  <si>
+    <t>BOOTH 240</t>
+  </si>
+  <si>
+    <t>BOOTH 241</t>
+  </si>
+  <si>
+    <t>BOOTH 242</t>
+  </si>
+  <si>
+    <t>BOOTH 243</t>
+  </si>
+  <si>
+    <t>BOOTH 244</t>
+  </si>
+  <si>
+    <t>BOOTH 245</t>
+  </si>
+  <si>
+    <t>BOOTH 246</t>
+  </si>
+  <si>
+    <t>BOOTH 247</t>
+  </si>
+  <si>
+    <t>BOOTH 248</t>
+  </si>
+  <si>
+    <t>BOOTH 249</t>
+  </si>
+  <si>
+    <t>BOOTH 250</t>
+  </si>
+  <si>
+    <t>BOOTH 251</t>
+  </si>
+  <si>
+    <t>BOOTH 252</t>
+  </si>
+  <si>
+    <t>BOOTH 253</t>
+  </si>
+  <si>
+    <t>BOOTH 254</t>
+  </si>
+  <si>
+    <t>BOOTH 255</t>
+  </si>
+  <si>
+    <t>BOOTH 256</t>
+  </si>
+  <si>
+    <t>BOOTH 257</t>
+  </si>
+  <si>
+    <t>BOOTH 258</t>
+  </si>
+  <si>
+    <t>BOOTH 259</t>
+  </si>
+  <si>
+    <t>BOOTH 260</t>
+  </si>
+  <si>
+    <t>BOOTH 261</t>
+  </si>
+  <si>
+    <t>BOOTH 262</t>
+  </si>
+  <si>
+    <t>BOOTH 263</t>
+  </si>
+  <si>
+    <t>BOOTH 264</t>
+  </si>
+  <si>
+    <t>BOOTH 265</t>
+  </si>
+  <si>
+    <t>BOOTH 266</t>
+  </si>
+  <si>
+    <t>BOOTH 267</t>
+  </si>
+  <si>
+    <t>BOOTH 268</t>
+  </si>
+  <si>
+    <t>BOOTH 269</t>
+  </si>
+  <si>
+    <t>BOOTH 270</t>
+  </si>
+  <si>
+    <t>BOOTH 271</t>
+  </si>
+  <si>
+    <t>BOOTH 272</t>
+  </si>
+  <si>
+    <t>BOOTH 273</t>
+  </si>
+  <si>
+    <t>BOOTH 274</t>
+  </si>
+  <si>
+    <t>BOOTH 275</t>
+  </si>
+  <si>
+    <t>BOOTH 276</t>
+  </si>
+  <si>
+    <t>BOOTH 277</t>
+  </si>
+  <si>
+    <t>BOOTH 278</t>
+  </si>
+  <si>
+    <t>BOOTH 279</t>
+  </si>
+  <si>
+    <t>BOOTH 280</t>
+  </si>
+  <si>
+    <t>BOOTH 281</t>
+  </si>
+  <si>
+    <t>BOOTH 282</t>
+  </si>
+  <si>
+    <t>BOOTH 283</t>
+  </si>
+  <si>
+    <t>BOOTH 284</t>
+  </si>
+  <si>
+    <t>BOOTH 285</t>
+  </si>
+  <si>
+    <t>BOOTH 286</t>
+  </si>
+  <si>
+    <t>BOOTH 287</t>
+  </si>
+  <si>
+    <t>BOOTH 288</t>
+  </si>
+  <si>
+    <t>BOOTH 289</t>
+  </si>
+  <si>
+    <t>BOOTH 290</t>
+  </si>
+  <si>
+    <t>BOOTH 291</t>
+  </si>
+  <si>
+    <t>BOOTH 292</t>
+  </si>
+  <si>
+    <t>BOOTH 293</t>
+  </si>
+  <si>
+    <t>BOOTH 294</t>
+  </si>
+  <si>
+    <t>BOOTH 295</t>
+  </si>
+  <si>
+    <t>BOOTH 296</t>
+  </si>
+  <si>
+    <t>BOOTH 297</t>
+  </si>
+  <si>
+    <t>BOOTH 298</t>
+  </si>
+  <si>
+    <t>BOOTH 299</t>
+  </si>
+  <si>
+    <t>BOOTH 300</t>
+  </si>
+  <si>
+    <t>BOOTH 301</t>
+  </si>
+  <si>
+    <t>BOOTH 302</t>
+  </si>
+  <si>
+    <t>BOOTH 303</t>
+  </si>
+  <si>
+    <t>BOOTH 304</t>
+  </si>
+  <si>
+    <t>BOOTH 305</t>
+  </si>
+  <si>
+    <t>BOOTH 306</t>
+  </si>
+  <si>
+    <t>BOOTH 307</t>
+  </si>
+  <si>
+    <t>BOOTH 308</t>
+  </si>
+  <si>
+    <t>BOOTH 309</t>
+  </si>
+  <si>
+    <t>BOOTH 310</t>
+  </si>
+  <si>
+    <t>BOOTH 311</t>
+  </si>
+  <si>
+    <t>BOOTH 312</t>
+  </si>
+  <si>
+    <t>BOOTH 313</t>
+  </si>
+  <si>
+    <t>BOOTH 314</t>
+  </si>
+  <si>
+    <t>BOOTH 315</t>
+  </si>
+  <si>
+    <t>BOOTH 316</t>
+  </si>
+  <si>
+    <t>BOOTH 317</t>
+  </si>
+  <si>
+    <t>BOOTH 318</t>
+  </si>
+  <si>
+    <t>BOOTH 319</t>
+  </si>
+  <si>
+    <t>BOOTH 320</t>
+  </si>
+  <si>
+    <t>BOOTH 321</t>
+  </si>
+  <si>
+    <t>BOOTH 322</t>
+  </si>
+  <si>
+    <t>BOOTH 323</t>
+  </si>
+  <si>
+    <t>BOOTH 324</t>
+  </si>
+  <si>
+    <t>BOOTH 325</t>
+  </si>
+  <si>
+    <t>BOOTH 326</t>
+  </si>
+  <si>
+    <t>BOOTH 327</t>
+  </si>
+  <si>
+    <t>BOOTH 328</t>
+  </si>
+  <si>
+    <t>BOOTH 329</t>
+  </si>
+  <si>
+    <t>BOOTH 330</t>
+  </si>
+  <si>
+    <t>BOOTH 331</t>
+  </si>
+  <si>
+    <t>BOOTH 332</t>
+  </si>
+  <si>
+    <t>BOOTH 333</t>
+  </si>
+  <si>
+    <t>BOOTH 334</t>
+  </si>
+  <si>
+    <t>BOOTH 335</t>
+  </si>
+  <si>
+    <t>BOOTH 336</t>
+  </si>
+  <si>
+    <t>BOOTH 337</t>
+  </si>
+  <si>
+    <t>BOOTH 338</t>
+  </si>
+  <si>
+    <t>BOOTH 339</t>
+  </si>
+  <si>
+    <t>BOOTH 340</t>
+  </si>
+  <si>
+    <t>BOOTH 341</t>
+  </si>
+  <si>
+    <t>BOOTH 342</t>
+  </si>
+  <si>
+    <t>BOOTH 343</t>
+  </si>
+  <si>
+    <t>BOOTH 344</t>
+  </si>
+  <si>
+    <t>BOOTH 345</t>
+  </si>
+  <si>
+    <t>BOOTH 346</t>
+  </si>
+  <si>
+    <t>BOOTH 347</t>
+  </si>
+  <si>
+    <t>BOOTH 348</t>
+  </si>
+  <si>
+    <t>BOOTH 349</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM NO. 350</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM NO. 351</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM NO. 352</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM NO. 353</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM NO. 354</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM NO. 355</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 356</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 357</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 358</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 359</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 360</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 361</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 362</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 363</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 364</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 365</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 366</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 367</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 368</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 369</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 370</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 371</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 372</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 373</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 374</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 375</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 376</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 377</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 378</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 379</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 380</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 381</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 382</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 383</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 384</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 385</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 386</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 387</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 388</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 389</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 390</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 391</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 392</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 393</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 394</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 395</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 396</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 397</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 398</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 399</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 400</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 401</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 402</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 408</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 409</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 410</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 411</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 416</t>
+  </si>
+  <si>
+    <t>BOOTH 349 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 417</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -434,8 +1418,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -451,7 +1443,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -459,12 +1451,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -763,85 +1773,157 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>444</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>445</v>
       </c>
       <c r="E2" t="s">
-        <v>118</v>
+        <v>446</v>
       </c>
       <c r="F2" t="s">
-        <v>119</v>
+        <v>447</v>
       </c>
       <c r="G2" t="s">
-        <v>120</v>
+        <v>448</v>
       </c>
       <c r="H2" t="s">
-        <v>121</v>
+        <v>449</v>
       </c>
       <c r="I2" t="s">
-        <v>122</v>
+        <v>450</v>
       </c>
       <c r="J2" t="s">
-        <v>123</v>
+        <v>451</v>
       </c>
       <c r="K2" t="s">
-        <v>124</v>
+        <v>452</v>
       </c>
       <c r="L2" t="s">
-        <v>125</v>
+        <v>453</v>
       </c>
       <c r="M2" t="s">
-        <v>126</v>
+        <v>454</v>
       </c>
       <c r="N2" t="s">
-        <v>127</v>
+        <v>455</v>
       </c>
       <c r="O2" t="s">
-        <v>128</v>
+        <v>456</v>
       </c>
       <c r="P2" t="s">
-        <v>129</v>
+        <v>457</v>
       </c>
       <c r="Q2" t="s">
-        <v>130</v>
+        <v>458</v>
       </c>
       <c r="R2" t="s">
-        <v>131</v>
+        <v>459</v>
       </c>
       <c r="S2" t="s">
-        <v>132</v>
+        <v>460</v>
       </c>
       <c r="T2" t="s">
-        <v>133</v>
+        <v>461</v>
       </c>
       <c r="U2" t="s">
-        <v>134</v>
+        <v>462</v>
       </c>
       <c r="V2" t="s">
-        <v>135</v>
+        <v>463</v>
       </c>
       <c r="W2" t="s">
-        <v>135</v>
+        <v>463</v>
       </c>
       <c r="X2" t="s">
-        <v>136</v>
+        <v>464</v>
       </c>
       <c r="Y2" t="s">
-        <v>137</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -849,7 +1931,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>526</v>
@@ -926,7 +2008,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>1010</v>
@@ -1003,7 +2085,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>744</v>
@@ -1080,7 +2162,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>1042</v>
@@ -1157,7 +2239,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>481</v>
@@ -1234,7 +2316,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>449</v>
@@ -1311,7 +2393,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>824</v>
@@ -1388,7 +2470,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>450</v>
@@ -1465,7 +2547,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <v>1020</v>
@@ -1542,7 +2624,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>1162</v>
@@ -1619,7 +2701,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>1113</v>
@@ -1696,7 +2778,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C14">
         <v>919</v>
@@ -1773,7 +2855,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <v>735</v>
@@ -1850,7 +2932,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C16">
         <v>705</v>
@@ -1927,7 +3009,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C17">
         <v>506</v>
@@ -2004,7 +3086,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="C18">
         <v>720</v>
@@ -2081,7 +3163,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="C19">
         <v>747</v>
@@ -2158,7 +3240,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="C20">
         <v>598</v>
@@ -2235,7 +3317,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C21">
         <v>874</v>
@@ -2312,7 +3394,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C22">
         <v>826</v>
@@ -2389,7 +3471,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="C23">
         <v>677</v>
@@ -2466,7 +3548,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C24">
         <v>701</v>
@@ -2543,7 +3625,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C25">
         <v>1184</v>
@@ -2620,7 +3702,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="C26">
         <v>613</v>
@@ -2697,7 +3779,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="C27">
         <v>828</v>
@@ -2774,7 +3856,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="C28">
         <v>821</v>
@@ -2851,7 +3933,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="C29">
         <v>638</v>
@@ -2928,7 +4010,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C30">
         <v>994</v>
@@ -3005,7 +4087,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="C31">
         <v>1142</v>
@@ -3082,7 +4164,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="C32">
         <v>579</v>
@@ -3159,7 +4241,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="C33">
         <v>866</v>
@@ -3236,7 +4318,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="C34">
         <v>718</v>
@@ -3313,7 +4395,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="C35">
         <v>512</v>
@@ -3390,7 +4472,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="C36">
         <v>1017</v>
@@ -3467,7 +4549,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="C37">
         <v>797</v>
@@ -3544,7 +4626,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="C38">
         <v>1121</v>
@@ -3621,7 +4703,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C39">
         <v>1140</v>
@@ -3698,7 +4780,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C40">
         <v>1125</v>
@@ -3775,7 +4857,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="C41">
         <v>1105</v>
@@ -3852,7 +4934,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="C42">
         <v>690</v>
@@ -3929,7 +5011,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="C43">
         <v>907</v>
@@ -4006,7 +5088,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="C44">
         <v>671</v>
@@ -4083,7 +5165,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="C45">
         <v>1170</v>
@@ -4160,7 +5242,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="C46">
         <v>990</v>
@@ -4237,7 +5319,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="C47">
         <v>345</v>
@@ -4314,7 +5396,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="C48">
         <v>784</v>
@@ -4391,7 +5473,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="C49">
         <v>789</v>
@@ -4468,7 +5550,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="C50">
         <v>746</v>
@@ -4545,7 +5627,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="C51">
         <v>718</v>
@@ -4622,7 +5704,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="C52">
         <v>707</v>
@@ -4699,7 +5781,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="C53">
         <v>710</v>
@@ -4776,7 +5858,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="C54">
         <v>736</v>
@@ -4853,7 +5935,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="C55">
         <v>1069</v>
@@ -4930,7 +6012,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="C56">
         <v>1180</v>
@@ -5007,7 +6089,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="C57">
         <v>1121</v>
@@ -5084,7 +6166,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="C58">
         <v>833</v>
@@ -5161,7 +6243,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="C59">
         <v>751</v>
@@ -5238,7 +6320,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="C60">
         <v>993</v>
@@ -5315,7 +6397,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="C61">
         <v>1068</v>
@@ -5392,7 +6474,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="C62">
         <v>1020</v>
@@ -5469,7 +6551,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="C63">
         <v>1109</v>
@@ -5546,7 +6628,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="C64">
         <v>368</v>
@@ -5623,7 +6705,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="C65">
         <v>651</v>
@@ -5700,7 +6782,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="C66">
         <v>600</v>
@@ -5777,7 +6859,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="C67">
         <v>1194</v>
@@ -5854,7 +6936,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="C68">
         <v>1031</v>
@@ -5931,7 +7013,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="C69">
         <v>850</v>
@@ -6008,7 +7090,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="C70">
         <v>937</v>
@@ -6085,7 +7167,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="C71">
         <v>761</v>
@@ -6162,7 +7244,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="C72">
         <v>1021</v>
@@ -6239,7 +7321,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="C73">
         <v>642</v>
@@ -6316,7 +7398,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="C74">
         <v>1131</v>
@@ -6393,7 +7475,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="C75">
         <v>861</v>
@@ -6470,7 +7552,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="C76">
         <v>638</v>
@@ -6547,7 +7629,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="C77">
         <v>879</v>
@@ -6624,7 +7706,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="C78">
         <v>607</v>
@@ -6701,7 +7783,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="C79">
         <v>617</v>
@@ -6778,7 +7860,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="C80">
         <v>404</v>
@@ -6855,7 +7937,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="C81">
         <v>957</v>
@@ -6932,7 +8014,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="C82">
         <v>848</v>
@@ -7009,7 +8091,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="C83">
         <v>511</v>
@@ -7086,7 +8168,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="C84">
         <v>736</v>
@@ -7163,7 +8245,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="C85">
         <v>418</v>
@@ -7240,7 +8322,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="C86">
         <v>969</v>
@@ -7317,7 +8399,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="C87">
         <v>688</v>
@@ -7394,7 +8476,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="C88">
         <v>821</v>
@@ -7471,7 +8553,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C89">
         <v>749</v>
@@ -7548,7 +8630,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="C90">
         <v>488</v>
@@ -7625,7 +8707,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="C91">
         <v>882</v>
@@ -7702,7 +8784,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="C92">
         <v>853</v>
@@ -7779,7 +8861,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="C93">
         <v>767</v>
@@ -7856,7 +8938,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="C94">
         <v>1110</v>
@@ -7933,7 +9015,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="C95">
         <v>667</v>
@@ -8010,7 +9092,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>41</v>
+        <v>120</v>
       </c>
       <c r="C96">
         <v>656</v>
@@ -8087,7 +9169,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>42</v>
+        <v>121</v>
       </c>
       <c r="C97">
         <v>1127</v>
@@ -8164,7 +9246,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="C98">
         <v>977</v>
@@ -8241,7 +9323,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>9</v>
+        <v>123</v>
       </c>
       <c r="C99">
         <v>1116</v>
@@ -8318,7 +9400,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>9</v>
+        <v>124</v>
       </c>
       <c r="C100">
         <v>1163</v>
@@ -8395,7 +9477,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="C101">
         <v>1126</v>
@@ -8472,7 +9554,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="C102">
         <v>1126</v>
@@ -8549,7 +9631,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>44</v>
+        <v>127</v>
       </c>
       <c r="C103">
         <v>797</v>
@@ -8626,7 +9708,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="C104">
         <v>1196</v>
@@ -8703,7 +9785,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>8</v>
+        <v>129</v>
       </c>
       <c r="C105">
         <v>1045</v>
@@ -8780,7 +9862,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="C106">
         <v>1133</v>
@@ -8857,7 +9939,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="C107">
         <v>909</v>
@@ -8934,7 +10016,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>46</v>
+        <v>132</v>
       </c>
       <c r="C108">
         <v>906</v>
@@ -9011,7 +10093,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>47</v>
+        <v>133</v>
       </c>
       <c r="C109">
         <v>583</v>
@@ -9088,7 +10170,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="C110">
         <v>902</v>
@@ -9165,7 +10247,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="C111">
         <v>1053</v>
@@ -9242,7 +10324,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="C112">
         <v>1080</v>
@@ -9319,7 +10401,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>46</v>
+        <v>137</v>
       </c>
       <c r="C113">
         <v>964</v>
@@ -9396,7 +10478,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>46</v>
+        <v>138</v>
       </c>
       <c r="C114">
         <v>889</v>
@@ -9473,7 +10555,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="C115">
         <v>1097</v>
@@ -9550,7 +10632,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="C116">
         <v>1036</v>
@@ -9627,7 +10709,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="C117">
         <v>932</v>
@@ -9704,7 +10786,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="C118">
         <v>847</v>
@@ -9781,7 +10863,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>16</v>
+        <v>143</v>
       </c>
       <c r="C119">
         <v>820</v>
@@ -9858,7 +10940,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>51</v>
+        <v>144</v>
       </c>
       <c r="C120">
         <v>1064</v>
@@ -9935,7 +11017,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>51</v>
+        <v>145</v>
       </c>
       <c r="C121">
         <v>1105</v>
@@ -10012,7 +11094,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="C122">
         <v>1095</v>
@@ -10089,7 +11171,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="C123">
         <v>710</v>
@@ -10166,7 +11248,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="C124">
         <v>689</v>
@@ -10243,7 +11325,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>52</v>
+        <v>149</v>
       </c>
       <c r="C125">
         <v>1124</v>
@@ -10320,7 +11402,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="C126">
         <v>1138</v>
@@ -10397,7 +11479,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>52</v>
+        <v>151</v>
       </c>
       <c r="C127">
         <v>1197</v>
@@ -10474,7 +11556,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>52</v>
+        <v>152</v>
       </c>
       <c r="C128">
         <v>963</v>
@@ -10551,7 +11633,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="C129">
         <v>659</v>
@@ -10628,7 +11710,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="C130">
         <v>665</v>
@@ -10705,7 +11787,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>52</v>
+        <v>155</v>
       </c>
       <c r="C131">
         <v>1127</v>
@@ -10782,7 +11864,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="C132">
         <v>1179</v>
@@ -10859,7 +11941,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>53</v>
+        <v>157</v>
       </c>
       <c r="C133">
         <v>849</v>
@@ -10936,7 +12018,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>54</v>
+        <v>158</v>
       </c>
       <c r="C134">
         <v>696</v>
@@ -11013,7 +12095,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>55</v>
+        <v>159</v>
       </c>
       <c r="C135">
         <v>1101</v>
@@ -11090,7 +12172,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="C136">
         <v>542</v>
@@ -11167,7 +12249,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>55</v>
+        <v>161</v>
       </c>
       <c r="C137">
         <v>728</v>
@@ -11244,7 +12326,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>55</v>
+        <v>162</v>
       </c>
       <c r="C138">
         <v>591</v>
@@ -11321,7 +12403,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>56</v>
+        <v>163</v>
       </c>
       <c r="C139">
         <v>1087</v>
@@ -11398,7 +12480,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>56</v>
+        <v>164</v>
       </c>
       <c r="C140">
         <v>788</v>
@@ -11475,7 +12557,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>56</v>
+        <v>165</v>
       </c>
       <c r="C141">
         <v>736</v>
@@ -11552,7 +12634,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>9</v>
+        <v>166</v>
       </c>
       <c r="C142">
         <v>670</v>
@@ -11629,7 +12711,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="C143">
         <v>1075</v>
@@ -11706,7 +12788,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="C144">
         <v>1174</v>
@@ -11783,7 +12865,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>53</v>
+        <v>169</v>
       </c>
       <c r="C145">
         <v>1040</v>
@@ -11860,7 +12942,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>53</v>
+        <v>170</v>
       </c>
       <c r="C146">
         <v>926</v>
@@ -11937,7 +13019,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>57</v>
+        <v>171</v>
       </c>
       <c r="C147">
         <v>1165</v>
@@ -12014,7 +13096,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="C148">
         <v>1132</v>
@@ -12091,7 +13173,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>54</v>
+        <v>173</v>
       </c>
       <c r="C149">
         <v>646</v>
@@ -12168,7 +13250,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>54</v>
+        <v>174</v>
       </c>
       <c r="C150">
         <v>830</v>
@@ -12245,7 +13327,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>54</v>
+        <v>175</v>
       </c>
       <c r="C151">
         <v>856</v>
@@ -12322,7 +13404,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>57</v>
+        <v>176</v>
       </c>
       <c r="C152">
         <v>1158</v>
@@ -12399,7 +13481,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>57</v>
+        <v>177</v>
       </c>
       <c r="C153">
         <v>1118</v>
@@ -12476,7 +13558,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="C154">
         <v>524</v>
@@ -12553,7 +13635,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>54</v>
+        <v>179</v>
       </c>
       <c r="C155">
         <v>812</v>
@@ -12630,7 +13712,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>56</v>
+        <v>180</v>
       </c>
       <c r="C156">
         <v>989</v>
@@ -12707,7 +13789,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>56</v>
+        <v>181</v>
       </c>
       <c r="C157">
         <v>374</v>
@@ -12784,7 +13866,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>56</v>
+        <v>182</v>
       </c>
       <c r="C158">
         <v>1121</v>
@@ -12861,7 +13943,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>58</v>
+        <v>183</v>
       </c>
       <c r="C159">
         <v>1077</v>
@@ -12938,7 +14020,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="C160">
         <v>875</v>
@@ -13015,7 +14097,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>59</v>
+        <v>185</v>
       </c>
       <c r="C161">
         <v>716</v>
@@ -13092,7 +14174,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>58</v>
+        <v>186</v>
       </c>
       <c r="C162">
         <v>1215</v>
@@ -13169,7 +14251,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>58</v>
+        <v>187</v>
       </c>
       <c r="C163">
         <v>828</v>
@@ -13246,7 +14328,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>58</v>
+        <v>188</v>
       </c>
       <c r="C164">
         <v>1014</v>
@@ -13323,7 +14405,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>60</v>
+        <v>189</v>
       </c>
       <c r="C165">
         <v>896</v>
@@ -13400,7 +14482,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="C166">
         <v>892</v>
@@ -13477,7 +14559,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>60</v>
+        <v>191</v>
       </c>
       <c r="C167">
         <v>835</v>
@@ -13554,7 +14636,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>60</v>
+        <v>192</v>
       </c>
       <c r="C168">
         <v>1166</v>
@@ -13631,7 +14713,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>61</v>
+        <v>193</v>
       </c>
       <c r="C169">
         <v>1079</v>
@@ -13708,7 +14790,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>61</v>
+        <v>194</v>
       </c>
       <c r="C170">
         <v>1068</v>
@@ -13785,7 +14867,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>61</v>
+        <v>195</v>
       </c>
       <c r="C171">
         <v>1080</v>
@@ -13862,7 +14944,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>61</v>
+        <v>196</v>
       </c>
       <c r="C172">
         <v>888</v>
@@ -13939,7 +15021,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>62</v>
+        <v>197</v>
       </c>
       <c r="C173">
         <v>1067</v>
@@ -14016,7 +15098,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>62</v>
+        <v>198</v>
       </c>
       <c r="C174">
         <v>1173</v>
@@ -14093,7 +15175,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>63</v>
+        <v>199</v>
       </c>
       <c r="C175">
         <v>957</v>
@@ -14170,7 +15252,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>63</v>
+        <v>200</v>
       </c>
       <c r="C176">
         <v>891</v>
@@ -14247,7 +15329,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>63</v>
+        <v>201</v>
       </c>
       <c r="C177">
         <v>815</v>
@@ -14324,7 +15406,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>63</v>
+        <v>202</v>
       </c>
       <c r="C178">
         <v>775</v>
@@ -14401,7 +15483,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>63</v>
+        <v>203</v>
       </c>
       <c r="C179">
         <v>736</v>
@@ -14478,7 +15560,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>64</v>
+        <v>204</v>
       </c>
       <c r="C180">
         <v>690</v>
@@ -14555,7 +15637,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>64</v>
+        <v>205</v>
       </c>
       <c r="C181">
         <v>757</v>
@@ -14632,7 +15714,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>64</v>
+        <v>206</v>
       </c>
       <c r="C182">
         <v>827</v>
@@ -14709,7 +15791,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>65</v>
+        <v>207</v>
       </c>
       <c r="C183">
         <v>920</v>
@@ -14786,7 +15868,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>66</v>
+        <v>208</v>
       </c>
       <c r="C184">
         <v>850</v>
@@ -14863,7 +15945,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>66</v>
+        <v>209</v>
       </c>
       <c r="C185">
         <v>1133</v>
@@ -14940,7 +16022,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>65</v>
+        <v>210</v>
       </c>
       <c r="C186">
         <v>600</v>
@@ -15017,7 +16099,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>67</v>
+        <v>211</v>
       </c>
       <c r="C187">
         <v>869</v>
@@ -15094,7 +16176,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="C188">
         <v>885</v>
@@ -15171,7 +16253,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>65</v>
+        <v>213</v>
       </c>
       <c r="C189">
         <v>677</v>
@@ -15248,7 +16330,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>65</v>
+        <v>214</v>
       </c>
       <c r="C190">
         <v>666</v>
@@ -15325,7 +16407,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>65</v>
+        <v>215</v>
       </c>
       <c r="C191">
         <v>672</v>
@@ -15402,7 +16484,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>63</v>
+        <v>216</v>
       </c>
       <c r="C192">
         <v>698</v>
@@ -15479,7 +16561,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>65</v>
+        <v>217</v>
       </c>
       <c r="C193">
         <v>853</v>
@@ -15556,7 +16638,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>65</v>
+        <v>218</v>
       </c>
       <c r="C194">
         <v>623</v>
@@ -15633,7 +16715,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>65</v>
+        <v>219</v>
       </c>
       <c r="C195">
         <v>598</v>
@@ -15710,7 +16792,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>65</v>
+        <v>220</v>
       </c>
       <c r="C196">
         <v>1081</v>
@@ -15787,7 +16869,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>68</v>
+        <v>221</v>
       </c>
       <c r="C197">
         <v>706</v>
@@ -15864,7 +16946,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>68</v>
+        <v>222</v>
       </c>
       <c r="C198">
         <v>649</v>
@@ -15941,7 +17023,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>69</v>
+        <v>223</v>
       </c>
       <c r="C199">
         <v>1046</v>
@@ -16018,7 +17100,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>69</v>
+        <v>224</v>
       </c>
       <c r="C200">
         <v>1058</v>
@@ -16095,7 +17177,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>69</v>
+        <v>225</v>
       </c>
       <c r="C201">
         <v>863</v>
@@ -16172,7 +17254,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>70</v>
+        <v>226</v>
       </c>
       <c r="C202">
         <v>977</v>
@@ -16249,7 +17331,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>70</v>
+        <v>227</v>
       </c>
       <c r="C203">
         <v>773</v>
@@ -16326,7 +17408,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>70</v>
+        <v>228</v>
       </c>
       <c r="C204">
         <v>1144</v>
@@ -16403,7 +17485,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>70</v>
+        <v>229</v>
       </c>
       <c r="C205">
         <v>1136</v>
@@ -16480,7 +17562,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>25</v>
+        <v>230</v>
       </c>
       <c r="C206">
         <v>917</v>
@@ -16557,7 +17639,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>25</v>
+        <v>231</v>
       </c>
       <c r="C207">
         <v>791</v>
@@ -16634,7 +17716,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>25</v>
+        <v>232</v>
       </c>
       <c r="C208">
         <v>777</v>
@@ -16711,7 +17793,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>71</v>
+        <v>233</v>
       </c>
       <c r="C209">
         <v>850</v>
@@ -16788,7 +17870,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>71</v>
+        <v>234</v>
       </c>
       <c r="C210">
         <v>1178</v>
@@ -16865,7 +17947,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>71</v>
+        <v>235</v>
       </c>
       <c r="C211">
         <v>999</v>
@@ -16942,7 +18024,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>71</v>
+        <v>236</v>
       </c>
       <c r="C212">
         <v>1140</v>
@@ -17019,7 +18101,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>71</v>
+        <v>237</v>
       </c>
       <c r="C213">
         <v>1020</v>
@@ -17096,7 +18178,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>72</v>
+        <v>238</v>
       </c>
       <c r="C214">
         <v>952</v>
@@ -17173,7 +18255,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>72</v>
+        <v>239</v>
       </c>
       <c r="C215">
         <v>1009</v>
@@ -17250,7 +18332,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>73</v>
+        <v>240</v>
       </c>
       <c r="C216">
         <v>1049</v>
@@ -17327,7 +18409,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>73</v>
+        <v>241</v>
       </c>
       <c r="C217">
         <v>1095</v>
@@ -17404,7 +18486,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>72</v>
+        <v>242</v>
       </c>
       <c r="C218">
         <v>951</v>
@@ -17481,7 +18563,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>68</v>
+        <v>243</v>
       </c>
       <c r="C219">
         <v>1028</v>
@@ -17558,7 +18640,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>68</v>
+        <v>244</v>
       </c>
       <c r="C220">
         <v>1082</v>
@@ -17635,7 +18717,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>74</v>
+        <v>245</v>
       </c>
       <c r="C221">
         <v>834</v>
@@ -17712,7 +18794,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>68</v>
+        <v>246</v>
       </c>
       <c r="C222">
         <v>1197</v>
@@ -17789,7 +18871,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>67</v>
+        <v>247</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -17866,7 +18948,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>67</v>
+        <v>248</v>
       </c>
       <c r="C224">
         <v>555</v>
@@ -17943,7 +19025,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>67</v>
+        <v>249</v>
       </c>
       <c r="C225">
         <v>731</v>
@@ -18020,7 +19102,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>68</v>
+        <v>250</v>
       </c>
       <c r="C226">
         <v>1128</v>
@@ -18097,7 +19179,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>67</v>
+        <v>251</v>
       </c>
       <c r="C227">
         <v>788</v>
@@ -18174,7 +19256,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>67</v>
+        <v>252</v>
       </c>
       <c r="C228">
         <v>946</v>
@@ -18251,7 +19333,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>67</v>
+        <v>253</v>
       </c>
       <c r="C229">
         <v>1157</v>
@@ -18328,7 +19410,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>67</v>
+        <v>254</v>
       </c>
       <c r="C230">
         <v>635</v>
@@ -18405,7 +19487,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>67</v>
+        <v>255</v>
       </c>
       <c r="C231">
         <v>805</v>
@@ -18482,7 +19564,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>67</v>
+        <v>256</v>
       </c>
       <c r="C232">
         <v>763</v>
@@ -18559,7 +19641,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>67</v>
+        <v>257</v>
       </c>
       <c r="C233">
         <v>915</v>
@@ -18636,7 +19718,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>75</v>
+        <v>258</v>
       </c>
       <c r="C234">
         <v>1018</v>
@@ -18713,7 +19795,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>75</v>
+        <v>259</v>
       </c>
       <c r="C235">
         <v>778</v>
@@ -18790,7 +19872,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>76</v>
+        <v>260</v>
       </c>
       <c r="C236">
         <v>1036</v>
@@ -18867,7 +19949,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>77</v>
+        <v>261</v>
       </c>
       <c r="C237">
         <v>756</v>
@@ -18944,7 +20026,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>77</v>
+        <v>262</v>
       </c>
       <c r="C238">
         <v>630</v>
@@ -19021,7 +20103,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>76</v>
+        <v>263</v>
       </c>
       <c r="C239">
         <v>775</v>
@@ -19098,7 +20180,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>76</v>
+        <v>264</v>
       </c>
       <c r="C240">
         <v>1134</v>
@@ -19175,7 +20257,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>76</v>
+        <v>265</v>
       </c>
       <c r="C241">
         <v>1175</v>
@@ -19252,7 +20334,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="C242">
         <v>1164</v>
@@ -19329,7 +20411,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>78</v>
+        <v>267</v>
       </c>
       <c r="C243">
         <v>976</v>
@@ -19406,7 +20488,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>79</v>
+        <v>268</v>
       </c>
       <c r="C244">
         <v>858</v>
@@ -19483,7 +20565,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="C245">
         <v>693</v>
@@ -19560,7 +20642,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="C246">
         <v>742</v>
@@ -19637,7 +20719,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>80</v>
+        <v>271</v>
       </c>
       <c r="C247">
         <v>676</v>
@@ -19714,7 +20796,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>81</v>
+        <v>272</v>
       </c>
       <c r="C248">
         <v>944</v>
@@ -19791,7 +20873,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>81</v>
+        <v>273</v>
       </c>
       <c r="C249">
         <v>1138</v>
@@ -19868,7 +20950,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>81</v>
+        <v>274</v>
       </c>
       <c r="C250">
         <v>845</v>
@@ -19945,7 +21027,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>81</v>
+        <v>275</v>
       </c>
       <c r="C251">
         <v>490</v>
@@ -20022,7 +21104,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="C252">
         <v>1177</v>
@@ -20099,7 +21181,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="C253">
         <v>881</v>
@@ -20176,7 +21258,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="C254">
         <v>723</v>
@@ -20253,7 +21335,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="C255">
         <v>829</v>
@@ -20330,7 +21412,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="C256">
         <v>1207</v>
@@ -20407,7 +21489,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="C257">
         <v>907</v>
@@ -20484,7 +21566,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="C258">
         <v>858</v>
@@ -20561,7 +21643,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>77</v>
+        <v>283</v>
       </c>
       <c r="C259">
         <v>877</v>
@@ -20638,7 +21720,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>77</v>
+        <v>284</v>
       </c>
       <c r="C260">
         <v>913</v>
@@ -20715,7 +21797,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>83</v>
+        <v>285</v>
       </c>
       <c r="C261">
         <v>574</v>
@@ -20792,7 +21874,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>83</v>
+        <v>286</v>
       </c>
       <c r="C262">
         <v>715</v>
@@ -20869,7 +21951,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>77</v>
+        <v>287</v>
       </c>
       <c r="C263">
         <v>803</v>
@@ -20946,7 +22028,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>77</v>
+        <v>288</v>
       </c>
       <c r="C264">
         <v>732</v>
@@ -21023,7 +22105,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>84</v>
+        <v>289</v>
       </c>
       <c r="C265">
         <v>811</v>
@@ -21100,7 +22182,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>84</v>
+        <v>290</v>
       </c>
       <c r="C266">
         <v>1045</v>
@@ -21177,7 +22259,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>8</v>
+        <v>291</v>
       </c>
       <c r="C267">
         <v>1137</v>
@@ -21254,7 +22336,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>8</v>
+        <v>292</v>
       </c>
       <c r="C268">
         <v>961</v>
@@ -21331,7 +22413,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>85</v>
+        <v>293</v>
       </c>
       <c r="C269">
         <v>936</v>
@@ -21408,7 +22490,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>85</v>
+        <v>294</v>
       </c>
       <c r="C270">
         <v>865</v>
@@ -21485,7 +22567,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>85</v>
+        <v>295</v>
       </c>
       <c r="C271">
         <v>1045</v>
@@ -21562,7 +22644,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="C272">
         <v>414</v>
@@ -21639,7 +22721,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>83</v>
+        <v>297</v>
       </c>
       <c r="C273">
         <v>968</v>
@@ -21716,7 +22798,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>83</v>
+        <v>298</v>
       </c>
       <c r="C274">
         <v>729</v>
@@ -21793,7 +22875,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="C275">
         <v>800</v>
@@ -21870,7 +22952,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>86</v>
+        <v>300</v>
       </c>
       <c r="C276">
         <v>678</v>
@@ -21947,7 +23029,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>86</v>
+        <v>301</v>
       </c>
       <c r="C277">
         <v>726</v>
@@ -22024,7 +23106,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>77</v>
+        <v>302</v>
       </c>
       <c r="C278">
         <v>551</v>
@@ -22101,7 +23183,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>77</v>
+        <v>303</v>
       </c>
       <c r="C279">
         <v>972</v>
@@ -22178,7 +23260,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>86</v>
+        <v>304</v>
       </c>
       <c r="C280">
         <v>691</v>
@@ -22255,7 +23337,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>86</v>
+        <v>305</v>
       </c>
       <c r="C281">
         <v>801</v>
@@ -22332,7 +23414,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="C282">
         <v>1117</v>
@@ -22409,7 +23491,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>86</v>
+        <v>307</v>
       </c>
       <c r="C283">
         <v>951</v>
@@ -22486,7 +23568,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>86</v>
+        <v>308</v>
       </c>
       <c r="C284">
         <v>492</v>
@@ -22563,7 +23645,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>87</v>
+        <v>309</v>
       </c>
       <c r="C285">
         <v>644</v>
@@ -22640,7 +23722,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>87</v>
+        <v>310</v>
       </c>
       <c r="C286">
         <v>691</v>
@@ -22717,7 +23799,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>87</v>
+        <v>311</v>
       </c>
       <c r="C287">
         <v>595</v>
@@ -22794,7 +23876,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>88</v>
+        <v>312</v>
       </c>
       <c r="C288">
         <v>739</v>
@@ -22871,7 +23953,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>88</v>
+        <v>313</v>
       </c>
       <c r="C289">
         <v>1050</v>
@@ -22948,7 +24030,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>88</v>
+        <v>314</v>
       </c>
       <c r="C290">
         <v>1092</v>
@@ -23025,7 +24107,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>88</v>
+        <v>315</v>
       </c>
       <c r="C291">
         <v>563</v>
@@ -23102,7 +24184,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>85</v>
+        <v>316</v>
       </c>
       <c r="C292">
         <v>990</v>
@@ -23179,7 +24261,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>89</v>
+        <v>317</v>
       </c>
       <c r="C293">
         <v>1142</v>
@@ -23256,7 +24338,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>89</v>
+        <v>318</v>
       </c>
       <c r="C294">
         <v>715</v>
@@ -23333,7 +24415,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>89</v>
+        <v>319</v>
       </c>
       <c r="C295">
         <v>664</v>
@@ -23410,7 +24492,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>89</v>
+        <v>320</v>
       </c>
       <c r="C296">
         <v>804</v>
@@ -23487,7 +24569,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>89</v>
+        <v>321</v>
       </c>
       <c r="C297">
         <v>592</v>
@@ -23564,7 +24646,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>89</v>
+        <v>322</v>
       </c>
       <c r="C298">
         <v>1095</v>
@@ -23641,7 +24723,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>90</v>
+        <v>323</v>
       </c>
       <c r="C299">
         <v>1052</v>
@@ -23718,7 +24800,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>90</v>
+        <v>324</v>
       </c>
       <c r="C300">
         <v>962</v>
@@ -23795,7 +24877,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>90</v>
+        <v>325</v>
       </c>
       <c r="C301">
         <v>729</v>
@@ -23872,7 +24954,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>91</v>
+        <v>326</v>
       </c>
       <c r="C302">
         <v>1221</v>
@@ -23949,7 +25031,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>91</v>
+        <v>327</v>
       </c>
       <c r="C303">
         <v>1116</v>
@@ -24026,7 +25108,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>92</v>
+        <v>328</v>
       </c>
       <c r="C304">
         <v>731</v>
@@ -24103,7 +25185,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>92</v>
+        <v>329</v>
       </c>
       <c r="C305">
         <v>575</v>
@@ -24180,7 +25262,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>92</v>
+        <v>330</v>
       </c>
       <c r="C306">
         <v>994</v>
@@ -24257,7 +25339,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>92</v>
+        <v>331</v>
       </c>
       <c r="C307">
         <v>1205</v>
@@ -24334,7 +25416,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>92</v>
+        <v>332</v>
       </c>
       <c r="C308">
         <v>1128</v>
@@ -24411,7 +25493,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>92</v>
+        <v>333</v>
       </c>
       <c r="C309">
         <v>785</v>
@@ -24488,7 +25570,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>92</v>
+        <v>334</v>
       </c>
       <c r="C310">
         <v>1020</v>
@@ -24565,7 +25647,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>92</v>
+        <v>335</v>
       </c>
       <c r="C311">
         <v>886</v>
@@ -24642,7 +25724,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>92</v>
+        <v>336</v>
       </c>
       <c r="C312">
         <v>688</v>
@@ -24719,7 +25801,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>92</v>
+        <v>337</v>
       </c>
       <c r="C313">
         <v>1085</v>
@@ -24796,7 +25878,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>92</v>
+        <v>338</v>
       </c>
       <c r="C314">
         <v>606</v>
@@ -24873,7 +25955,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>92</v>
+        <v>339</v>
       </c>
       <c r="C315">
         <v>631</v>
@@ -24950,7 +26032,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>90</v>
+        <v>340</v>
       </c>
       <c r="C316">
         <v>1013</v>
@@ -25027,7 +26109,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>93</v>
+        <v>341</v>
       </c>
       <c r="C317">
         <v>1017</v>
@@ -25104,7 +26186,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>93</v>
+        <v>342</v>
       </c>
       <c r="C318">
         <v>930</v>
@@ -25181,7 +26263,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>93</v>
+        <v>343</v>
       </c>
       <c r="C319">
         <v>1180</v>
@@ -25258,7 +26340,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>94</v>
+        <v>344</v>
       </c>
       <c r="C320">
         <v>762</v>
@@ -25335,7 +26417,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>94</v>
+        <v>345</v>
       </c>
       <c r="C321">
         <v>611</v>
@@ -25412,7 +26494,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>94</v>
+        <v>346</v>
       </c>
       <c r="C322">
         <v>821</v>
@@ -25489,7 +26571,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>95</v>
+        <v>347</v>
       </c>
       <c r="C323">
         <v>1041</v>
@@ -25566,7 +26648,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>95</v>
+        <v>348</v>
       </c>
       <c r="C324">
         <v>1125</v>
@@ -25643,7 +26725,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>95</v>
+        <v>349</v>
       </c>
       <c r="C325">
         <v>929</v>
@@ -25720,7 +26802,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>95</v>
+        <v>350</v>
       </c>
       <c r="C326">
         <v>1060</v>
@@ -25797,7 +26879,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>94</v>
+        <v>351</v>
       </c>
       <c r="C327">
         <v>505</v>
@@ -25874,7 +26956,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>16</v>
+        <v>352</v>
       </c>
       <c r="C328">
         <v>1077</v>
@@ -25951,7 +27033,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>96</v>
+        <v>353</v>
       </c>
       <c r="C329">
         <v>999</v>
@@ -26028,7 +27110,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>16</v>
+        <v>354</v>
       </c>
       <c r="C330">
         <v>786</v>
@@ -26105,7 +27187,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>16</v>
+        <v>355</v>
       </c>
       <c r="C331">
         <v>781</v>
@@ -26182,7 +27264,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>97</v>
+        <v>356</v>
       </c>
       <c r="C332">
         <v>1136</v>
@@ -26259,7 +27341,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>97</v>
+        <v>357</v>
       </c>
       <c r="C333">
         <v>1006</v>
@@ -26336,7 +27418,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>98</v>
+        <v>358</v>
       </c>
       <c r="C334">
         <v>1106</v>
@@ -26413,7 +27495,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>99</v>
+        <v>359</v>
       </c>
       <c r="C335">
         <v>736</v>
@@ -26490,7 +27572,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>98</v>
+        <v>360</v>
       </c>
       <c r="C336">
         <v>812</v>
@@ -26567,7 +27649,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>98</v>
+        <v>361</v>
       </c>
       <c r="C337">
         <v>1165</v>
@@ -26644,7 +27726,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>98</v>
+        <v>362</v>
       </c>
       <c r="C338">
         <v>1158</v>
@@ -26721,7 +27803,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>98</v>
+        <v>363</v>
       </c>
       <c r="C339">
         <v>989</v>
@@ -26798,7 +27880,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>98</v>
+        <v>364</v>
       </c>
       <c r="C340">
         <v>1003</v>
@@ -26875,7 +27957,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>98</v>
+        <v>365</v>
       </c>
       <c r="C341">
         <v>776</v>
@@ -26952,7 +28034,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>98</v>
+        <v>366</v>
       </c>
       <c r="C342">
         <v>1175</v>
@@ -27029,7 +28111,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>99</v>
+        <v>367</v>
       </c>
       <c r="C343">
         <v>1119</v>
@@ -27106,7 +28188,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>99</v>
+        <v>368</v>
       </c>
       <c r="C344">
         <v>910</v>
@@ -27183,7 +28265,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>99</v>
+        <v>369</v>
       </c>
       <c r="C345">
         <v>714</v>
@@ -27260,7 +28342,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>99</v>
+        <v>370</v>
       </c>
       <c r="C346">
         <v>996</v>
@@ -27337,7 +28419,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>99</v>
+        <v>371</v>
       </c>
       <c r="C347">
         <v>1050</v>
@@ -27414,7 +28496,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>99</v>
+        <v>372</v>
       </c>
       <c r="C348">
         <v>1188</v>
@@ -27491,7 +28573,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>99</v>
+        <v>373</v>
       </c>
       <c r="C349">
         <v>979</v>
@@ -27568,7 +28650,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>99</v>
+        <v>374</v>
       </c>
       <c r="C350">
         <v>1171</v>
@@ -27645,7 +28727,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>99</v>
+        <v>375</v>
       </c>
       <c r="C351">
         <v>1075</v>
@@ -27722,7 +28804,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>99</v>
+        <v>376</v>
       </c>
       <c r="C352">
         <v>717</v>
@@ -27799,7 +28881,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>99</v>
+        <v>377</v>
       </c>
       <c r="C353">
         <v>777</v>
@@ -27876,7 +28958,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>99</v>
+        <v>378</v>
       </c>
       <c r="C354">
         <v>756</v>
@@ -27953,7 +29035,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>100</v>
+        <v>379</v>
       </c>
       <c r="C355">
         <v>1206</v>
@@ -28030,7 +29112,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>100</v>
+        <v>380</v>
       </c>
       <c r="C356">
         <v>989</v>
@@ -28107,7 +29189,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>101</v>
+        <v>381</v>
       </c>
       <c r="C357">
         <v>846</v>
@@ -28184,7 +29266,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>101</v>
+        <v>382</v>
       </c>
       <c r="C358">
         <v>642</v>
@@ -28261,7 +29343,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>102</v>
+        <v>383</v>
       </c>
       <c r="C359">
         <v>1003</v>
@@ -28338,7 +29420,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>102</v>
+        <v>384</v>
       </c>
       <c r="C360">
         <v>1082</v>
@@ -28415,7 +29497,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>102</v>
+        <v>385</v>
       </c>
       <c r="C361">
         <v>1030</v>
@@ -28492,7 +29574,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>102</v>
+        <v>386</v>
       </c>
       <c r="C362">
         <v>797</v>
@@ -28569,7 +29651,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>102</v>
+        <v>387</v>
       </c>
       <c r="C363">
         <v>1121</v>
@@ -28646,7 +29728,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>102</v>
+        <v>388</v>
       </c>
       <c r="C364">
         <v>1056</v>
@@ -28723,7 +29805,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>39</v>
+        <v>389</v>
       </c>
       <c r="C365">
         <v>629</v>
@@ -28800,7 +29882,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>39</v>
+        <v>390</v>
       </c>
       <c r="C366">
         <v>1201</v>
@@ -28877,7 +29959,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>39</v>
+        <v>391</v>
       </c>
       <c r="C367">
         <v>1155</v>
@@ -28954,7 +30036,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>39</v>
+        <v>392</v>
       </c>
       <c r="C368">
         <v>1099</v>
@@ -29031,7 +30113,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>39</v>
+        <v>393</v>
       </c>
       <c r="C369">
         <v>956</v>
@@ -29108,7 +30190,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>103</v>
+        <v>394</v>
       </c>
       <c r="C370">
         <v>593</v>
@@ -29185,7 +30267,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>103</v>
+        <v>395</v>
       </c>
       <c r="C371">
         <v>903</v>
@@ -29262,7 +30344,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>104</v>
+        <v>396</v>
       </c>
       <c r="C372">
         <v>993</v>
@@ -29339,7 +30421,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>104</v>
+        <v>397</v>
       </c>
       <c r="C373">
         <v>1010</v>
@@ -29416,7 +30498,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>105</v>
+        <v>398</v>
       </c>
       <c r="C374">
         <v>984</v>
@@ -29493,7 +30575,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>105</v>
+        <v>399</v>
       </c>
       <c r="C375">
         <v>1018</v>
@@ -29570,7 +30652,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>103</v>
+        <v>400</v>
       </c>
       <c r="C376">
         <v>1208</v>
@@ -29647,7 +30729,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>9</v>
+        <v>401</v>
       </c>
       <c r="C377">
         <v>1121</v>
@@ -29724,7 +30806,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>9</v>
+        <v>402</v>
       </c>
       <c r="C378">
         <v>1032</v>
@@ -29801,7 +30883,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>8</v>
+        <v>403</v>
       </c>
       <c r="C379">
         <v>672</v>
@@ -29878,7 +30960,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>8</v>
+        <v>404</v>
       </c>
       <c r="C380">
         <v>622</v>
@@ -29955,7 +31037,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>106</v>
+        <v>405</v>
       </c>
       <c r="C381">
         <v>1117</v>
@@ -30032,7 +31114,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>106</v>
+        <v>406</v>
       </c>
       <c r="C382">
         <v>982</v>
@@ -30109,7 +31191,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>106</v>
+        <v>407</v>
       </c>
       <c r="C383">
         <v>802</v>
@@ -30186,7 +31268,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>7</v>
+        <v>408</v>
       </c>
       <c r="C384">
         <v>1228</v>
@@ -30263,7 +31345,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>7</v>
+        <v>409</v>
       </c>
       <c r="C385">
         <v>959</v>
@@ -30340,7 +31422,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>16</v>
+        <v>410</v>
       </c>
       <c r="C386">
         <v>848</v>
@@ -30417,7 +31499,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>16</v>
+        <v>411</v>
       </c>
       <c r="C387">
         <v>677</v>
@@ -30494,7 +31576,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>41</v>
+        <v>412</v>
       </c>
       <c r="C388">
         <v>722</v>
@@ -30571,7 +31653,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>41</v>
+        <v>413</v>
       </c>
       <c r="C389">
         <v>883</v>
@@ -30648,7 +31730,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>107</v>
+        <v>414</v>
       </c>
       <c r="C390">
         <v>1135</v>
@@ -30725,7 +31807,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>108</v>
+        <v>415</v>
       </c>
       <c r="C391">
         <v>512</v>
@@ -30802,7 +31884,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>25</v>
+        <v>416</v>
       </c>
       <c r="C392">
         <v>1075</v>
@@ -30879,7 +31961,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>107</v>
+        <v>417</v>
       </c>
       <c r="C393">
         <v>1082</v>
@@ -30956,7 +32038,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>109</v>
+        <v>418</v>
       </c>
       <c r="C394">
         <v>1074</v>
@@ -31033,7 +32115,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>110</v>
+        <v>419</v>
       </c>
       <c r="C395">
         <v>1170</v>
@@ -31110,7 +32192,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>69</v>
+        <v>420</v>
       </c>
       <c r="C396">
         <v>1125</v>
@@ -31187,7 +32269,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>69</v>
+        <v>421</v>
       </c>
       <c r="C397">
         <v>1210</v>
@@ -31264,7 +32346,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>8</v>
+        <v>422</v>
       </c>
       <c r="C398">
         <v>977</v>
@@ -31341,7 +32423,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>8</v>
+        <v>423</v>
       </c>
       <c r="C399">
         <v>575</v>
@@ -31418,7 +32500,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>9</v>
+        <v>424</v>
       </c>
       <c r="C400">
         <v>599</v>
@@ -31495,7 +32577,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>9</v>
+        <v>425</v>
       </c>
       <c r="C401">
         <v>689</v>
@@ -31572,7 +32654,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>8</v>
+        <v>426</v>
       </c>
       <c r="C402">
         <v>905</v>
@@ -31649,7 +32731,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>9</v>
+        <v>427</v>
       </c>
       <c r="C403">
         <v>1215</v>
@@ -31726,7 +32808,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>111</v>
+        <v>428</v>
       </c>
       <c r="C404">
         <v>1078</v>
@@ -31803,7 +32885,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>111</v>
+        <v>429</v>
       </c>
       <c r="C405">
         <v>529</v>
@@ -31880,7 +32962,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>112</v>
+        <v>430</v>
       </c>
       <c r="C406">
         <v>608</v>
@@ -31957,7 +33039,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>112</v>
+        <v>431</v>
       </c>
       <c r="C407">
         <v>1013</v>
@@ -32034,7 +33116,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>39</v>
+        <v>432</v>
       </c>
       <c r="C408">
         <v>976</v>
@@ -32111,7 +33193,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>18</v>
+        <v>433</v>
       </c>
       <c r="C409">
         <v>1236</v>
@@ -32188,7 +33270,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>100</v>
+        <v>434</v>
       </c>
       <c r="C410">
         <v>466</v>
@@ -32265,7 +33347,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>113</v>
+        <v>435</v>
       </c>
       <c r="C411">
         <v>1031</v>
@@ -32342,7 +33424,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>113</v>
+        <v>436</v>
       </c>
       <c r="C412">
         <v>741</v>
@@ -32419,7 +33501,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>114</v>
+        <v>437</v>
       </c>
       <c r="C413">
         <v>1140</v>
@@ -32496,7 +33578,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>114</v>
+        <v>438</v>
       </c>
       <c r="C414">
         <v>813</v>
@@ -32573,7 +33655,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>115</v>
+        <v>439</v>
       </c>
       <c r="C415">
         <v>980</v>
@@ -32650,7 +33732,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>115</v>
+        <v>440</v>
       </c>
       <c r="C416">
         <v>773</v>
@@ -32727,7 +33809,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>9</v>
+        <v>441</v>
       </c>
       <c r="C417">
         <v>808</v>
@@ -32804,7 +33886,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>9</v>
+        <v>442</v>
       </c>
       <c r="C418">
         <v>733</v>
@@ -32881,7 +33963,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="C419">
         <v>1144</v>
